--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-21T15:27:12+00:00</t>
+    <t>2024-10-22T10:27:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-22T10:27:39+00:00</t>
+    <t>2024-10-22T15:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-22T15:26:51+00:00</t>
+    <t>2024-10-23T04:30:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-23T04:30:12+00:00</t>
+    <t>2024-10-23T15:28:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-23T15:28:11+00:00</t>
+    <t>2024-10-24T04:29:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-24T04:29:26+00:00</t>
+    <t>2024-10-24T15:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-24T15:26:50+00:00</t>
+    <t>2024-10-25T04:31:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T04:31:08+00:00</t>
+    <t>2024-10-25T07:51:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T07:51:12+00:00</t>
+    <t>2024-10-25T15:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T15:09:58+00:00</t>
+    <t>2024-10-26T04:29:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T04:29:20+00:00</t>
+    <t>2024-10-26T08:59:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T08:59:08+00:00</t>
+    <t>2024-10-26T09:30:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T09:30:33+00:00</t>
+    <t>2024-10-26T10:09:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T10:09:34+00:00</t>
+    <t>2024-10-26T12:22:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T12:22:56+00:00</t>
+    <t>2024-10-26T15:42:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T15:42:52+00:00</t>
+    <t>2024-10-26T16:45:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T16:45:55+00:00</t>
+    <t>2024-10-27T04:29:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T04:29:11+00:00</t>
+    <t>2024-10-27T10:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T10:26:12+00:00</t>
+    <t>2024-10-27T15:25:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T15:25:18+00:00</t>
+    <t>2024-10-28T04:30:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T04:30:48+00:00</t>
+    <t>2024-10-28T10:27:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T10:27:26+00:00</t>
+    <t>2024-10-28T12:01:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T12:01:29+00:00</t>
+    <t>2024-10-28T15:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T15:27:17+00:00</t>
+    <t>2024-10-29T04:29:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T04:29:45+00:00</t>
+    <t>2024-10-29T10:28:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T10:28:20+00:00</t>
+    <t>2024-10-29T15:28:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T15:28:01+00:00</t>
+    <t>2024-10-30T04:30:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T04:30:40+00:00</t>
+    <t>2024-10-30T10:27:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T10:27:34+00:00</t>
+    <t>2024-10-30T15:26:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T15:26:52+00:00</t>
+    <t>2024-10-31T04:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T04:31:02+00:00</t>
+    <t>2024-10-31T10:27:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T10:27:14+00:00</t>
+    <t>2024-10-31T15:27:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T15:27:42+00:00</t>
+    <t>2024-11-01T04:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-01T04:28:44+00:00</t>
+    <t>2024-11-01T10:26:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-01T10:26:46+00:00</t>
+    <t>2024-11-01T15:26:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-01T15:26:21+00:00</t>
+    <t>2024-11-02T04:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-02T04:28:40+00:00</t>
+    <t>2024-11-02T10:24:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-02T10:24:33+00:00</t>
+    <t>2024-11-02T15:26:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-02T15:26:54+00:00</t>
+    <t>2024-11-03T04:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T04:28:29+00:00</t>
+    <t>2024-11-03T10:28:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T10:28:45+00:00</t>
+    <t>2024-11-03T15:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T15:24:31+00:00</t>
+    <t>2024-11-04T04:29:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T04:29:56+00:00</t>
+    <t>2024-11-04T09:04:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T09:04:35+00:00</t>
+    <t>2024-11-04T10:28:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T10:28:47+00:00</t>
+    <t>2024-11-04T15:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T15:27:53+00:00</t>
+    <t>2024-11-04T16:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T16:28:37+00:00</t>
+    <t>2024-11-05T04:28:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T04:28:41+00:00</t>
+    <t>2024-11-05T10:28:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T10:28:51+00:00</t>
+    <t>2024-11-05T15:26:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T15:26:29+00:00</t>
+    <t>2024-11-06T04:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/main/ValueSet-JDV-bdpm-all.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T04:31:09+00:00</t>
+    <t>2024-11-06T10:27:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
